--- a/scrapper-vw/input.xlsx
+++ b/scrapper-vw/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ELFANI\scrapper-brand\scrapper-vw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F2CD62-74E0-4678-A8B6-E9FFD96D084B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6017659F-7AE9-4DDF-A682-3FF42BAF2DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE9D63A0-45ED-4AA7-85F4-ACF2438FD00C}"/>
   </bookViews>
